--- a/INSTANCES/instances_xlsx/A_MTN_2/196FL_7A_4.xlsx
+++ b/INSTANCES/instances_xlsx/A_MTN_2/196FL_7A_4.xlsx
@@ -17,6 +17,7 @@
     <sheet name="Parameters" r:id="rId4" sheetId="2"/>
     <sheet name="M_stations" r:id="rId5" sheetId="3"/>
     <sheet name="Aircrafts" r:id="rId6" sheetId="4"/>
+    <sheet name="Coefficients" r:id="rId8" sheetId="5"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -28,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="87">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="99">
   <si>
     <t>YEAR</t>
   </si>
@@ -289,6 +290,42 @@
   </si>
   <si>
     <t>TK_DAY</t>
+  </si>
+  <si>
+    <t>FH_TK_MIN</t>
+  </si>
+  <si>
+    <t>FH_TK_MAX</t>
+  </si>
+  <si>
+    <t>FH_TK_MEDIAN</t>
+  </si>
+  <si>
+    <t>FH_TK_MEAN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MIN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MAX</t>
+  </si>
+  <si>
+    <t>FH_DAY_MEDIAN</t>
+  </si>
+  <si>
+    <t>FH_DAY_MEAN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MIN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MAX</t>
+  </si>
+  <si>
+    <t>TK_DAY_MEDIAN</t>
+  </si>
+  <si>
+    <t>TK_DAY_MEAN</t>
   </si>
 </sst>
 </file>
@@ -6703,7 +6740,7 @@
         <v>0</v>
       </c>
       <c r="D3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E3">
         <v>1</v>
@@ -6720,7 +6757,7 @@
         <v>0</v>
       </c>
       <c r="D4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E4">
         <v>1</v>
@@ -6754,7 +6791,7 @@
         <v>0</v>
       </c>
       <c r="D6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E6">
         <v>1</v>
@@ -6771,7 +6808,7 @@
         <v>0</v>
       </c>
       <c r="D7">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -6788,10 +6825,96 @@
         <v>0</v>
       </c>
       <c r="D8">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E8">
         <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
+  <dimension ref="A1:L2"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:12">
+      <c r="A1" t="s">
+        <v>87</v>
+      </c>
+      <c r="B1" t="s">
+        <v>88</v>
+      </c>
+      <c r="C1" t="s">
+        <v>89</v>
+      </c>
+      <c r="D1" t="s">
+        <v>90</v>
+      </c>
+      <c r="E1" t="s">
+        <v>91</v>
+      </c>
+      <c r="F1" t="s">
+        <v>92</v>
+      </c>
+      <c r="G1" t="s">
+        <v>93</v>
+      </c>
+      <c r="H1" t="s">
+        <v>94</v>
+      </c>
+      <c r="I1" t="s">
+        <v>95</v>
+      </c>
+      <c r="J1" t="s">
+        <v>96</v>
+      </c>
+      <c r="K1" t="s">
+        <v>97</v>
+      </c>
+      <c r="L1" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12">
+      <c r="A2">
+        <v>16</v>
+      </c>
+      <c r="B2">
+        <v>377</v>
+      </c>
+      <c r="C2">
+        <v>154</v>
+      </c>
+      <c r="D2">
+        <v>165</v>
+      </c>
+      <c r="E2">
+        <v>229</v>
+      </c>
+      <c r="F2">
+        <v>1079</v>
+      </c>
+      <c r="G2">
+        <v>672</v>
+      </c>
+      <c r="H2">
+        <v>661</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="J2">
+        <v>7</v>
+      </c>
+      <c r="K2">
+        <v>4</v>
+      </c>
+      <c r="L2">
+        <v>4</v>
       </c>
     </row>
   </sheetData>
